--- a/Result/profitability/1454.xlsx
+++ b/Result/profitability/1454.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.05</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.18875</v>
+        <v>-0.215</v>
       </c>
       <c r="N2" t="n">
-        <v>3.29625</v>
+        <v>2.83625</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -681,7 +681,7 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.18</v>
+        <v>-0.18875</v>
       </c>
       <c r="N3" t="n">
-        <v>3.40125</v>
+        <v>3.28</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.18</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.14</v>
+        <v>-0.1575</v>
       </c>
       <c r="N4" t="n">
-        <v>4.04</v>
+        <v>3.585</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.06</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.13875</v>
+        <v>-0.1</v>
       </c>
       <c r="N5" t="n">
-        <v>3.95625</v>
+        <v>3.83375</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>-0.12</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.08875</v>
+        <v>-0.10125</v>
       </c>
       <c r="N6" t="n">
-        <v>3.75375</v>
+        <v>4.3825</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,13 +1264,13 @@
         <v>-0.06</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.08249999999999999</v>
+        <v>-0.05625</v>
       </c>
       <c r="N7" t="n">
-        <v>5.3575</v>
+        <v>5.762500000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
@@ -1282,7 +1282,7 @@
         <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.06</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0225</v>
+        <v>-0.02375</v>
       </c>
       <c r="N8" t="n">
-        <v>6.201250000000001</v>
+        <v>6.06125</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>0.05</v>
       </c>
       <c r="M9" t="n">
-        <v>0.008750000000000003</v>
+        <v>0.008749999999999999</v>
       </c>
       <c r="N9" t="n">
         <v>6.693750000000001</v>
@@ -1645,7 +1645,7 @@
         <v>-0.08</v>
       </c>
       <c r="M10" t="n">
-        <v>0.005000000000000003</v>
+        <v>0.004999999999999999</v>
       </c>
       <c r="N10" t="n">
         <v>6.545</v>
@@ -1772,7 +1772,7 @@
         <v>-0.02</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.006249999999999999</v>
+        <v>-0.006250000000000002</v>
       </c>
       <c r="N11" t="n">
         <v>6.62</v>
@@ -2026,7 +2026,7 @@
         <v>0.09</v>
       </c>
       <c r="M13" t="n">
-        <v>0.001250000000000001</v>
+        <v>0.001249999999999998</v>
       </c>
       <c r="N13" t="n">
         <v>6.6675</v>
@@ -9846,6 +9846,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1454</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>347</v>
+      </c>
+      <c r="D75" t="n">
+        <v>338</v>
+      </c>
+      <c r="E75" t="n">
+        <v>9</v>
+      </c>
+      <c r="F75" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-30</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-8.63%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>3</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-27</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-26</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.20875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>2.945</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.009999999999999981</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.04999999999999982</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-1.12</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.2947368421052631</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.3100000000000001</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.5961538461538463</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-0.98</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.26775956284153</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
